--- a/artfynd/A 33243-2026 artfynd.xlsx
+++ b/artfynd/A 33243-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,32 +680,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>95992800</v>
+        <v>136616258</v>
       </c>
       <c r="B2" t="n">
-        <v>56876</v>
+        <v>43243</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208257</v>
+        <v>101070</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Silversmygare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Hesperia comma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,36 +713,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>trafikdödad</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Amnevägen 5, Otterbäcken, Gullspång, Vg</t>
+          <t>Otterbäcken, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>444899</v>
+        <v>445013</v>
       </c>
       <c r="R2" t="n">
-        <v>6534928</v>
+        <v>6535286</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -769,12 +749,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>C260302 (NVI Calluna AB)</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,24 +774,375 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Robert Roffey</t>
+          <t>Jonas Mattsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Robert Roffey</t>
+          <t>Erik Edvardsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136616258</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>136616303</v>
+      </c>
+      <c r="B3" t="n">
+        <v>56935</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>208255</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Skogsödla</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Zootoca vivipara</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Jacquin, 1787)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Otterbäcken, Vg</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>445006</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6535320</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Gullspång</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Amnehärad</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>C260302 (NVI Calluna AB)</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Jonas Mattsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Erik Edvardsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136616303</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>95992800</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56876</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>208257</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kopparödla</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Anguis fragilis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>trafikdödad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Amnevägen 5, Otterbäcken, Gullspång, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>444899</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6534928</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gullspång</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Amnehärad</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2021-09-09</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2021-09-09</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Robert Roffey</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Robert Roffey</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/95992800</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136616283</v>
+      </c>
+      <c r="B5" t="n">
+        <v>56927</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>208257</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kopparödla</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Anguis fragilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Otterbäcken, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>444822</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6535013</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gullspång</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Amnehärad</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>C260302 (NVI Calluna AB)</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jonas Mattsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Erik Edvardsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136616283</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33243-2026 artfynd.xlsx
+++ b/artfynd/A 33243-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136616258</v>
       </c>
       <c r="B2" t="n">
-        <v>43243</v>
+        <v>43245</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136616303</v>
       </c>
       <c r="B3" t="n">
-        <v>56935</v>
+        <v>56937</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136616283</v>
       </c>
       <c r="B5" t="n">
-        <v>56927</v>
+        <v>56929</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 33243-2026 artfynd.xlsx
+++ b/artfynd/A 33243-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136616258</v>
       </c>
       <c r="B2" t="n">
-        <v>43245</v>
+        <v>43258</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136616303</v>
       </c>
       <c r="B3" t="n">
-        <v>56937</v>
+        <v>56950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136616283</v>
       </c>
       <c r="B5" t="n">
-        <v>56929</v>
+        <v>56942</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 33243-2026 artfynd.xlsx
+++ b/artfynd/A 33243-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136616258</v>
       </c>
       <c r="B2" t="n">
-        <v>43258</v>
+        <v>43260</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136616303</v>
       </c>
       <c r="B3" t="n">
-        <v>56950</v>
+        <v>56952</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136616283</v>
       </c>
       <c r="B5" t="n">
-        <v>56942</v>
+        <v>56944</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
